--- a/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
@@ -325,50 +325,52 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TEA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>127402</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100111948-043</t>
+          <t>0100112437-005</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN BA RIA - VUNG TAU</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502550210</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>35000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3500.0</v>
+        <v>2000.0</v>
       </c>
       <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O7" s="13" t="n">
-        <v>38500.0</v>
+        <v>22000.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -386,6 +388,636 @@
         </is>
       </c>
       <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>406066</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>10000.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>11000.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>406130</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>08/08/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>412706</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>09/08/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>50000.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>5000.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>55000.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>470275</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>473524</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>15/08/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>514973</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>25/08/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>K25TEA</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>519296</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+        </is>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>20000.0</v>
+      </c>
+      <c r="L14" s="13" t="n">
+        <v>2000.0</v>
+      </c>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>22000.0</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>K25THA</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>988505</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>04/08/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>0106869738-044</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>394545.0</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>39455.0</v>
+      </c>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13" t="n">
+        <v>434000.0</v>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
@@ -325,52 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>406027</t>
+          <t>4695799</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M7" s="13"/>
-      <c r="N7" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -404,52 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>406066</t>
+          <t>4695801</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>10000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M8" s="13"/>
-      <c r="N8" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>11000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -483,52 +479,50 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>406130</t>
+          <t>4890445</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>08/08/2025</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -562,52 +556,50 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>412706</t>
+          <t>4995875</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>09/08/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>50000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>5000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M10" s="13"/>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>55000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -641,52 +633,50 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>470275</t>
+          <t>5066533</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>14/08/2025</t>
+          <t>15/08/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M11" s="13"/>
-      <c r="N11" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -720,52 +710,50 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>473524</t>
+          <t>5134885</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>20/08/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M12" s="13"/>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -799,52 +787,50 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>514973</t>
+          <t>5250317</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>25/08/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M13" s="13"/>
-      <c r="N13" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -878,12 +864,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>K25TEA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>519296</t>
+          <t>5250318</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -893,37 +879,35 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0100112437-005</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Vũng Tàu </t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CT CP DT XAY DUNG TM DV KY THUAT H &amp; V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>20000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>2000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M14" s="13"/>
-      <c r="N14" s="13" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>22000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -957,50 +941,50 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>K25THA</t>
+          <t>K25TBB</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>988505</t>
+          <t>5278488</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0106869738-044</t>
+          <t>0100233488</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
         </is>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502551856</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Đầu Tư Xây Dựng Thương Mại Dịch Vụ Kỹ Thuật H Và V</t>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>394545.0</v>
+        <v>15000.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>39455.0</v>
+        <v>1500.0</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>434000.0</v>
+        <v>16500.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1018,6 +1002,83 @@
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>K25TBB</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>5313366</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>30/08/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>0100233488</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+        </is>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>15000.0</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1500.0</v>
+      </c>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13" t="n">
+        <v>16500.0</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>

--- a/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
+++ b/Hoadon/HDVao/8/HDDienTuKhongMa.xlsx
@@ -325,59 +325,59 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>4695799</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100150619-006</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
         </is>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CTY TNHH DAI LY TAU BIEN VUNG TAU</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>15000.0</v>
+        <v>2.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1500.0</v>
+        <v>0.2</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>16500.0</v>
+        <v>2.2</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>26342.5</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -402,50 +402,50 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TAA</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>4695801</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100150619-006</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Bà Rịa - Vũng Tàu</t>
         </is>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CTY TNHH DAI LY TAU BIEN VUNG TAU</t>
         </is>
       </c>
       <c r="K8" s="13" t="n">
-        <v>15000.0</v>
+        <v>1995179.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1500.0</v>
+        <v>199519.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>16500.0</v>
+        <v>2194698.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -479,50 +479,50 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>4890445</t>
+          <t>277515</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>04/08/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>15000.0</v>
+        <v>139427.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1500.0</v>
+        <v>13943.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>16500.0</v>
+        <v>153370.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -556,50 +556,50 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>4995875</t>
+          <t>298509</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K10" s="13" t="n">
-        <v>15000.0</v>
+        <v>140020.0</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>1500.0</v>
+        <v>14002.0</v>
       </c>
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>16500.0</v>
+        <v>154022.0</v>
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
@@ -633,50 +633,50 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>5066533</t>
+          <t>319018</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>15/08/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>15000.0</v>
+        <v>168500.0</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1500.0</v>
+        <v>16850.0</v>
       </c>
       <c r="M11" s="13"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13" t="n">
-        <v>16500.0</v>
+        <v>185350.0</v>
       </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
@@ -710,50 +710,50 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25DAA</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>5134885</t>
+          <t>319209</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>20/08/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0100686209-129</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 8 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K12" s="13" t="n">
-        <v>15000.0</v>
+        <v>140909.0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1500.0</v>
+        <v>14091.0</v>
       </c>
       <c r="M12" s="13"/>
       <c r="N12" s="13"/>
       <c r="O12" s="13" t="n">
-        <v>16500.0</v>
+        <v>155000.0</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -787,50 +787,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TAN</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>5250317</t>
+          <t>163491</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0104093672</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
-        </is>
-      </c>
-      <c r="H13" s="6"/>
+          <t>TỔNG CÔNG TY CP BƯU CHÍNH VIETTEL</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 2, ngõ 15 phố Duy Tân, Phường Cầu Giấy, Thành Phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>15000.0</v>
+        <v>31944.0</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1500.0</v>
-      </c>
-      <c r="M13" s="13"/>
+        <v>2556.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="N13" s="13"/>
       <c r="O13" s="13" t="n">
-        <v>16500.0</v>
+        <v>34500.0</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -864,50 +870,50 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25THA</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>5250318</t>
+          <t>971421</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>04/08/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0106869738-044</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>TRUNG TÂM KINH DOANH VNPT BÀ RỊA - VŨNG TÀU - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
         </is>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K14" s="13" t="n">
-        <v>15000.0</v>
+        <v>123461.0</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>1500.0</v>
+        <v>12346.0</v>
       </c>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="n">
-        <v>16500.0</v>
+        <v>135807.0</v>
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
@@ -941,50 +947,50 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TDA</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>5278488</t>
+          <t>908818</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>28/08/2025</t>
+          <t>03/08/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>0300951119-010</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
+          <t>CHI NHÁNH TỔNG CÔNG TY ĐIỆN LỰC THÀNH PHỐ HỒ CHÍ MINH TNHH - CÔNG TY ĐIỆN LỰC VŨNG TÀU</t>
         </is>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>15000.0</v>
+        <v>1415248.0</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1500.0</v>
+        <v>113220.0</v>
       </c>
       <c r="M15" s="13"/>
       <c r="N15" s="13"/>
       <c r="O15" s="13" t="n">
-        <v>16500.0</v>
+        <v>1528468.0</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
@@ -1018,50 +1024,54 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>K25TBB</t>
+          <t>K25TXT</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>5313366</t>
+          <t>356996</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>30/08/2025</t>
+          <t>06/08/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>0100233488</t>
+          <t>3500102573</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Ngân Hàng Thương mại Cổ phần Quốc Tế Việt Nam</t>
-        </is>
-      </c>
-      <c r="H16" s="6"/>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502551856</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K16" s="13" t="n">
-        <v>15000.0</v>
+        <v>462963.0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>1500.0</v>
+        <v>37037.0</v>
       </c>
       <c r="M16" s="13"/>
       <c r="N16" s="13"/>
       <c r="O16" s="13" t="n">
-        <v>16500.0</v>
+        <v>500000.0</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
@@ -1079,6 +1089,249 @@
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>371714</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>14/08/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>377178</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>17/08/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>570630.0</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>45650.0</v>
+      </c>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13" t="n">
+        <v>616280.0</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>K25TXT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>392403</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>26/08/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3500102573</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 12 Hoàng Hoa Thám - Phường Vũng Tàu - TP Hồ Chí Minh - Việt Nam</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502217971</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>740741.0</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>59259.0</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
